--- a/server/data/registrations.xlsx
+++ b/server/data/registrations.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>Full Name</t>
   </si>
@@ -50,13 +50,31 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>[{"name":"Hello world","age":34,"relation":"Nephew","gender":"Male","tokenGiven":true}]</t>
-  </si>
-  <si>
-    <t>ddd</t>
-  </si>
-  <si>
-    <t>2026-05-16T06:53:40.142Z</t>
+    <t>[{"name":"aaa","age":23,"relation":"Grandmother","gender":"Male","tokenGiven":true},{"name":"vvvvv","age":23,"relation":"Nephew","tokenGiven":true}]</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2026-05-16T07:24:51.944Z</t>
+  </si>
+  <si>
+    <t>Harishbhai Chitroda</t>
+  </si>
+  <si>
+    <t>9898881391</t>
+  </si>
+  <si>
+    <t>defrf</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>[{"name":"bbbb","age":23,"relation":"Grandfather","gender":"Male","tokenGiven":true}]</t>
+  </si>
+  <si>
+    <t>2026-05-16T07:32:35.238Z</t>
   </si>
 </sst>
 </file>
@@ -437,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -493,6 +511,35 @@
       </c>
       <c r="I2" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/server/data/registrations.xlsx
+++ b/server/data/registrations.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>Full Name</t>
   </si>
@@ -26,6 +26,9 @@
   </si>
   <si>
     <t>Present Today</t>
+  </si>
+  <si>
+    <t>Token Given</t>
   </si>
   <si>
     <t>Members</t>
@@ -47,7 +50,7 @@
 Amroli, surat</t>
   </si>
   <si>
-    <t>Yes</t>
+    <t>No</t>
   </si>
   <si>
     <t>[{"name":"aaa","age":23,"relation":"Grandmother","gender":"Male","tokenGiven":true},{"name":"vvvvv","age":23,"relation":"Nephew","tokenGiven":true}]</t>
@@ -56,7 +59,7 @@
     <t/>
   </si>
   <si>
-    <t>2026-05-16T07:24:51.944Z</t>
+    <t>2026-05-17T07:42:40.809Z</t>
   </si>
   <si>
     <t>Harishbhai Chitroda</t>
@@ -68,13 +71,10 @@
     <t>defrf</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>[{"name":"bbbb","age":23,"relation":"Grandfather","gender":"Male","tokenGiven":true}]</t>
   </si>
   <si>
-    <t>2026-05-16T07:32:35.238Z</t>
+    <t>2026-05-17T07:42:40.810Z</t>
   </si>
 </sst>
 </file>
@@ -458,7 +458,7 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -482,17 +482,20 @@
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -501,27 +504,27 @@
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3">
         <v>4</v>
@@ -530,13 +533,13 @@
         <v>4</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
         <v>20</v>
